--- a/Thesis Forecasting/PAPER CONTEXT/tables/appendix_A_cleaned_dataset_summary.xlsx
+++ b/Thesis Forecasting/PAPER CONTEXT/tables/appendix_A_cleaned_dataset_summary.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
